--- a/spreadsheet/SIMS-Blog-Manager-template-Product5.2-Official-Lean.xlsx
+++ b/spreadsheet/SIMS-Blog-Manager-template-Product5.2-Official-Lean.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Home" sheetId="1" r:id="R3e03b85fe3df43d4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日の改善" sheetId="2" r:id="R958bdad103854315"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善中" sheetId="3" r:id="R2de633e2e39641c7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ブログ診断" sheetId="4" r:id="R21f43c88cbbc4003"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="処理ログ" sheetId="5" r:id="R3ab16e7120cb42c8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定" sheetId="6" r:id="R5a53a4176d154cba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SearchConsole_Data" sheetId="7" r:id="R1e0aa187150142d4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Improvement_Queue" sheetId="8" r:id="R9089f545a7fd4fb8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Improvement_Log" sheetId="9" r:id="Rb1218dc0bc8f4d3b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Home" sheetId="1" r:id="Rf5c4d8f7f324448d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日の改善" sheetId="2" r:id="R91c8f430188d4d0e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善中" sheetId="3" r:id="Rd507c5a4b7584a65"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ブログ診断" sheetId="4" r:id="Rc9fe5e41d2174e09"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="処理ログ" sheetId="5" r:id="Rd9c199017873473e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定" sheetId="6" r:id="Rd0723a1f0dd040f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SearchConsole_Data" sheetId="7" r:id="R9ba6cd90c71f4e44"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Improvement_Queue" sheetId="8" r:id="R798210b0b3e14188"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Improvement_Log" sheetId="9" r:id="Rd7e20c03bd2a41db"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -345,7 +345,7 @@
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="34" t="str">
-        <x:v>SIMS-Blog-Manager Product 5.2.0</x:v>
+        <x:v>SIMS-Blog-Manager Product 5.2.1</x:v>
       </x:c>
       <x:c r="B1" s="35"/>
       <x:c r="C1" s="35"/>
@@ -5313,7 +5313,7 @@
         <x:v>Product Version</x:v>
       </x:c>
       <x:c r="B2" t="str">
-        <x:v>5.2.0</x:v>
+        <x:v>5.2.1</x:v>
       </x:c>
       <x:c r="C2" t="str">
         <x:v>UI/UX改訂版。既存データ互換。</x:v>

--- a/spreadsheet/SIMS-Blog-Manager-template-Product5.2-Official-Lean.xlsx
+++ b/spreadsheet/SIMS-Blog-Manager-template-Product5.2-Official-Lean.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Home" sheetId="1" r:id="Rf5c4d8f7f324448d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日の改善" sheetId="2" r:id="R91c8f430188d4d0e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善中" sheetId="3" r:id="Rd507c5a4b7584a65"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ブログ診断" sheetId="4" r:id="Rc9fe5e41d2174e09"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="処理ログ" sheetId="5" r:id="Rd9c199017873473e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定" sheetId="6" r:id="Rd0723a1f0dd040f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SearchConsole_Data" sheetId="7" r:id="R9ba6cd90c71f4e44"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Improvement_Queue" sheetId="8" r:id="R798210b0b3e14188"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Improvement_Log" sheetId="9" r:id="Rd7e20c03bd2a41db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Home" sheetId="1" r:id="Rbe7c4e7370e34abe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日の改善" sheetId="2" r:id="R2312e73ef5d6468d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善中" sheetId="3" r:id="R243b131f10c84245"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ブログ診断" sheetId="4" r:id="Rd533778ea3bf4487"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="処理ログ" sheetId="5" r:id="R4651a34d1bff4b7f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定" sheetId="6" r:id="R14a198e3e655485b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SearchConsole_Data" sheetId="7" r:id="R80f5a83974e34628"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Improvement_Queue" sheetId="8" r:id="R8bb26cd4d07a4c21"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Improvement_Log" sheetId="9" r:id="R6c54539411914028"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -345,7 +345,7 @@
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="34" t="str">
-        <x:v>SIMS-Blog-Manager Product 5.2.1</x:v>
+        <x:v>SIMS-Blog-Manager Product 5.2.2</x:v>
       </x:c>
       <x:c r="B1" s="35"/>
       <x:c r="C1" s="35"/>
@@ -5313,7 +5313,7 @@
         <x:v>Product Version</x:v>
       </x:c>
       <x:c r="B2" t="str">
-        <x:v>5.2.1</x:v>
+        <x:v>5.2.2</x:v>
       </x:c>
       <x:c r="C2" t="str">
         <x:v>UI/UX改訂版。既存データ互換。</x:v>

--- a/spreadsheet/SIMS-Blog-Manager-template-Product5.2-Official-Lean.xlsx
+++ b/spreadsheet/SIMS-Blog-Manager-template-Product5.2-Official-Lean.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Home" sheetId="1" r:id="Rbe7c4e7370e34abe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日の改善" sheetId="2" r:id="R2312e73ef5d6468d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善中" sheetId="3" r:id="R243b131f10c84245"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ブログ診断" sheetId="4" r:id="Rd533778ea3bf4487"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="処理ログ" sheetId="5" r:id="R4651a34d1bff4b7f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定" sheetId="6" r:id="R14a198e3e655485b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SearchConsole_Data" sheetId="7" r:id="R80f5a83974e34628"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Improvement_Queue" sheetId="8" r:id="R8bb26cd4d07a4c21"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Improvement_Log" sheetId="9" r:id="R6c54539411914028"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Home" sheetId="1" r:id="Rc29e626b2a2e4463"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日の改善" sheetId="2" r:id="Rccdce90513c64d68"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善中" sheetId="3" r:id="R7e9a3558ed50433f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ブログ診断" sheetId="4" r:id="R4c236dcf2f184720"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="処理ログ" sheetId="5" r:id="Ra931c6feb32442db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定" sheetId="6" r:id="R9a2df8775cc244f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SearchConsole_Data" sheetId="7" r:id="Rb6e1c5f5c73e4589"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Improvement_Queue" sheetId="8" r:id="Rf4e44889986446ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Improvement_Log" sheetId="9" r:id="Rfb07acbdba43490c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -345,7 +345,7 @@
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="34" t="str">
-        <x:v>SIMS-Blog-Manager Product 5.2.2</x:v>
+        <x:v>SIMS-Blog-Manager Product 5.2.3</x:v>
       </x:c>
       <x:c r="B1" s="35"/>
       <x:c r="C1" s="35"/>
@@ -5313,7 +5313,7 @@
         <x:v>Product Version</x:v>
       </x:c>
       <x:c r="B2" t="str">
-        <x:v>5.2.2</x:v>
+        <x:v>5.2.3</x:v>
       </x:c>
       <x:c r="C2" t="str">
         <x:v>UI/UX改訂版。既存データ互換。</x:v>

--- a/spreadsheet/SIMS-Blog-Manager-template-Product5.2-Official-Lean.xlsx
+++ b/spreadsheet/SIMS-Blog-Manager-template-Product5.2-Official-Lean.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Home" sheetId="1" r:id="Rc29e626b2a2e4463"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日の改善" sheetId="2" r:id="Rccdce90513c64d68"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善中" sheetId="3" r:id="R7e9a3558ed50433f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ブログ診断" sheetId="4" r:id="R4c236dcf2f184720"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="処理ログ" sheetId="5" r:id="Ra931c6feb32442db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定" sheetId="6" r:id="R9a2df8775cc244f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SearchConsole_Data" sheetId="7" r:id="Rb6e1c5f5c73e4589"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Improvement_Queue" sheetId="8" r:id="Rf4e44889986446ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Improvement_Log" sheetId="9" r:id="Rfb07acbdba43490c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Home" sheetId="1" r:id="R3099d7b109d04605"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日の改善" sheetId="2" r:id="R7de594d27e2341ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善中" sheetId="3" r:id="R20a0d3123edd4e36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ブログ診断" sheetId="4" r:id="R31bbd7cb9c2d44c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="処理ログ" sheetId="5" r:id="R376d5812d9a94c40"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定" sheetId="6" r:id="Rc185f0a80c29439b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SearchConsole_Data" sheetId="7" r:id="Rad429a29654e40b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Improvement_Queue" sheetId="8" r:id="R5e0f5ea89f074f2a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Improvement_Log" sheetId="9" r:id="R3aaeea1946aa443a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -345,7 +345,7 @@
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="34" t="str">
-        <x:v>SIMS-Blog-Manager Product 5.2.3</x:v>
+        <x:v>SIMS-Blog-Manager Product 5.2.4</x:v>
       </x:c>
       <x:c r="B1" s="35"/>
       <x:c r="C1" s="35"/>
@@ -5313,7 +5313,7 @@
         <x:v>Product Version</x:v>
       </x:c>
       <x:c r="B2" t="str">
-        <x:v>5.2.3</x:v>
+        <x:v>5.2.4</x:v>
       </x:c>
       <x:c r="C2" t="str">
         <x:v>UI/UX改訂版。既存データ互換。</x:v>

--- a/spreadsheet/SIMS-Blog-Manager-template-Product5.2-Official-Lean.xlsx
+++ b/spreadsheet/SIMS-Blog-Manager-template-Product5.2-Official-Lean.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Home" sheetId="1" r:id="R3099d7b109d04605"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日の改善" sheetId="2" r:id="R7de594d27e2341ed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善中" sheetId="3" r:id="R20a0d3123edd4e36"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ブログ診断" sheetId="4" r:id="R31bbd7cb9c2d44c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="処理ログ" sheetId="5" r:id="R376d5812d9a94c40"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定" sheetId="6" r:id="Rc185f0a80c29439b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SearchConsole_Data" sheetId="7" r:id="Rad429a29654e40b7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Improvement_Queue" sheetId="8" r:id="R5e0f5ea89f074f2a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Improvement_Log" sheetId="9" r:id="R3aaeea1946aa443a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Home" sheetId="1" r:id="R31811e1ac8764369"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日の改善" sheetId="2" r:id="R109592e973784114"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善中" sheetId="3" r:id="R2f0f9a8cac8349ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ブログ診断" sheetId="4" r:id="R46c23bed8e954252"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="処理ログ" sheetId="5" r:id="R3f6562b08c4e4e56"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定" sheetId="6" r:id="R6b5a772228774c05"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SearchConsole_Data" sheetId="7" r:id="R37d906e857fd4e93"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Improvement_Queue" sheetId="8" r:id="R84abff6a38c949d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Improvement_Log" sheetId="9" r:id="Rf1c71970737d4525"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -345,7 +345,7 @@
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="34" t="str">
-        <x:v>SIMS-Blog-Manager Product 5.2.4</x:v>
+        <x:v>SIMS-Blog-Manager Product 5.2.5</x:v>
       </x:c>
       <x:c r="B1" s="35"/>
       <x:c r="C1" s="35"/>
@@ -5313,7 +5313,7 @@
         <x:v>Product Version</x:v>
       </x:c>
       <x:c r="B2" t="str">
-        <x:v>5.2.4</x:v>
+        <x:v>5.2.5</x:v>
       </x:c>
       <x:c r="C2" t="str">
         <x:v>UI/UX改訂版。既存データ互換。</x:v>

--- a/spreadsheet/SIMS-Blog-Manager-template-Product5.2-Official-Lean.xlsx
+++ b/spreadsheet/SIMS-Blog-Manager-template-Product5.2-Official-Lean.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Home" sheetId="1" r:id="R31811e1ac8764369"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日の改善" sheetId="2" r:id="R109592e973784114"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善中" sheetId="3" r:id="R2f0f9a8cac8349ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ブログ診断" sheetId="4" r:id="R46c23bed8e954252"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="処理ログ" sheetId="5" r:id="R3f6562b08c4e4e56"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定" sheetId="6" r:id="R6b5a772228774c05"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SearchConsole_Data" sheetId="7" r:id="R37d906e857fd4e93"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Improvement_Queue" sheetId="8" r:id="R84abff6a38c949d3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Improvement_Log" sheetId="9" r:id="Rf1c71970737d4525"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Home" sheetId="1" r:id="Rcfacbda4951d4a87"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日の改善" sheetId="2" r:id="R8cd886460974446c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善中" sheetId="3" r:id="R614f90fc3e834ec6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ブログ診断" sheetId="4" r:id="Rc88d4f2a8dd04a4a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="処理ログ" sheetId="5" r:id="R8ef21b87254e454c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定" sheetId="6" r:id="R864a2e3a4cb04339"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SearchConsole_Data" sheetId="7" r:id="R121ba76197934aac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Improvement_Queue" sheetId="8" r:id="Re3c11c64d2554895"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Improvement_Log" sheetId="9" r:id="R634d746ccfae4329"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -345,7 +345,7 @@
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="34" t="str">
-        <x:v>SIMS-Blog-Manager Product 5.2.5</x:v>
+        <x:v>SIMS-Blog-Manager Product 5.2.6</x:v>
       </x:c>
       <x:c r="B1" s="35"/>
       <x:c r="C1" s="35"/>
@@ -5313,7 +5313,7 @@
         <x:v>Product Version</x:v>
       </x:c>
       <x:c r="B2" t="str">
-        <x:v>5.2.5</x:v>
+        <x:v>5.2.6</x:v>
       </x:c>
       <x:c r="C2" t="str">
         <x:v>UI/UX改訂版。既存データ互換。</x:v>

--- a/spreadsheet/SIMS-Blog-Manager-template-Product5.2-Official-Lean.xlsx
+++ b/spreadsheet/SIMS-Blog-Manager-template-Product5.2-Official-Lean.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Home" sheetId="1" r:id="Rcfacbda4951d4a87"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日の改善" sheetId="2" r:id="R8cd886460974446c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善中" sheetId="3" r:id="R614f90fc3e834ec6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ブログ診断" sheetId="4" r:id="Rc88d4f2a8dd04a4a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="処理ログ" sheetId="5" r:id="R8ef21b87254e454c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定" sheetId="6" r:id="R864a2e3a4cb04339"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SearchConsole_Data" sheetId="7" r:id="R121ba76197934aac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Improvement_Queue" sheetId="8" r:id="Re3c11c64d2554895"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Improvement_Log" sheetId="9" r:id="R634d746ccfae4329"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Home" sheetId="1" r:id="R3076f021fbd44b05"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日の改善" sheetId="2" r:id="R1060c6c25ed94b1e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善中" sheetId="3" r:id="R3a664948911b4433"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ブログ診断" sheetId="4" r:id="R2a8136aa3c0b41e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="処理ログ" sheetId="5" r:id="Reced7b9095bc4ba9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定" sheetId="6" r:id="R29dd6f3227554752"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SearchConsole_Data" sheetId="7" r:id="R2701b9a1841d4555"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Improvement_Queue" sheetId="8" r:id="R8ca91de4f55f4077"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Improvement_Log" sheetId="9" r:id="Rbe33cfb3ea20435f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -345,7 +345,7 @@
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="34" t="str">
-        <x:v>SIMS-Blog-Manager Product 5.2.6</x:v>
+        <x:v>SIMS-Blog-Manager Product 5.2.7</x:v>
       </x:c>
       <x:c r="B1" s="35"/>
       <x:c r="C1" s="35"/>
@@ -5313,7 +5313,7 @@
         <x:v>Product Version</x:v>
       </x:c>
       <x:c r="B2" t="str">
-        <x:v>5.2.6</x:v>
+        <x:v>5.2.7</x:v>
       </x:c>
       <x:c r="C2" t="str">
         <x:v>UI/UX改訂版。既存データ互換。</x:v>

--- a/spreadsheet/SIMS-Blog-Manager-template-Product5.2-Official-Lean.xlsx
+++ b/spreadsheet/SIMS-Blog-Manager-template-Product5.2-Official-Lean.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Home" sheetId="1" r:id="R3076f021fbd44b05"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日の改善" sheetId="2" r:id="R1060c6c25ed94b1e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善中" sheetId="3" r:id="R3a664948911b4433"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ブログ診断" sheetId="4" r:id="R2a8136aa3c0b41e4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="処理ログ" sheetId="5" r:id="Reced7b9095bc4ba9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定" sheetId="6" r:id="R29dd6f3227554752"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SearchConsole_Data" sheetId="7" r:id="R2701b9a1841d4555"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Improvement_Queue" sheetId="8" r:id="R8ca91de4f55f4077"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Improvement_Log" sheetId="9" r:id="Rbe33cfb3ea20435f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Home" sheetId="1" r:id="Ra3175edd93074641"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日の改善" sheetId="2" r:id="Rd59802c7f1cb4a5e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善中" sheetId="3" r:id="R513dd4331fb243e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ブログ診断" sheetId="4" r:id="R3867461cddde4f32"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="処理ログ" sheetId="5" r:id="R8b9cf741ad524bdf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定" sheetId="6" r:id="Ra0cd72989dc34c97"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SearchConsole_Data" sheetId="7" r:id="R5633aaabdb9048b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Improvement_Queue" sheetId="8" r:id="R614b7898384d4f8f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Improvement_Log" sheetId="9" r:id="R776330c7bd41419d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -345,7 +345,7 @@
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="34" t="str">
-        <x:v>SIMS-Blog-Manager Product 5.2.7</x:v>
+        <x:v>SIMS-Blog-Manager Product 5.2.8</x:v>
       </x:c>
       <x:c r="B1" s="35"/>
       <x:c r="C1" s="35"/>
@@ -5313,7 +5313,7 @@
         <x:v>Product Version</x:v>
       </x:c>
       <x:c r="B2" t="str">
-        <x:v>5.2.7</x:v>
+        <x:v>5.2.8</x:v>
       </x:c>
       <x:c r="C2" t="str">
         <x:v>UI/UX改訂版。既存データ互換。</x:v>

--- a/spreadsheet/SIMS-Blog-Manager-template-Product5.2-Official-Lean.xlsx
+++ b/spreadsheet/SIMS-Blog-Manager-template-Product5.2-Official-Lean.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Home" sheetId="1" r:id="Ra3175edd93074641"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日の改善" sheetId="2" r:id="Rd59802c7f1cb4a5e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善中" sheetId="3" r:id="R513dd4331fb243e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ブログ診断" sheetId="4" r:id="R3867461cddde4f32"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="処理ログ" sheetId="5" r:id="R8b9cf741ad524bdf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定" sheetId="6" r:id="Ra0cd72989dc34c97"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SearchConsole_Data" sheetId="7" r:id="R5633aaabdb9048b4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Improvement_Queue" sheetId="8" r:id="R614b7898384d4f8f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Improvement_Log" sheetId="9" r:id="R776330c7bd41419d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Home" sheetId="1" r:id="Rbafb5a5aa06c4abd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日の改善" sheetId="2" r:id="Ra9d67e1293a44529"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善中" sheetId="3" r:id="R8e4944fa37af43a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ブログ診断" sheetId="4" r:id="Rd210eb2ee6264bb4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="処理ログ" sheetId="5" r:id="R06a33bda23024f3f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定" sheetId="6" r:id="R32a03964741045bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SearchConsole_Data" sheetId="7" r:id="Rcb33ba13a49e401b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Improvement_Queue" sheetId="8" r:id="Rfcac8f3d5eca46b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Improvement_Log" sheetId="9" r:id="Rbb5b327508364485"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -345,7 +345,7 @@
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="34" t="str">
-        <x:v>SIMS-Blog-Manager Product 5.2.8</x:v>
+        <x:v>SIMS-Blog-Manager Product 5.2.9</x:v>
       </x:c>
       <x:c r="B1" s="35"/>
       <x:c r="C1" s="35"/>
@@ -5313,7 +5313,7 @@
         <x:v>Product Version</x:v>
       </x:c>
       <x:c r="B2" t="str">
-        <x:v>5.2.8</x:v>
+        <x:v>5.2.9</x:v>
       </x:c>
       <x:c r="C2" t="str">
         <x:v>UI/UX改訂版。既存データ互換。</x:v>

--- a/spreadsheet/SIMS-Blog-Manager-template-Product5.2-Official-Lean.xlsx
+++ b/spreadsheet/SIMS-Blog-Manager-template-Product5.2-Official-Lean.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Home" sheetId="1" r:id="Rbafb5a5aa06c4abd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日の改善" sheetId="2" r:id="Ra9d67e1293a44529"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善中" sheetId="3" r:id="R8e4944fa37af43a3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ブログ診断" sheetId="4" r:id="Rd210eb2ee6264bb4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="処理ログ" sheetId="5" r:id="R06a33bda23024f3f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定" sheetId="6" r:id="R32a03964741045bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SearchConsole_Data" sheetId="7" r:id="Rcb33ba13a49e401b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Improvement_Queue" sheetId="8" r:id="Rfcac8f3d5eca46b5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Improvement_Log" sheetId="9" r:id="Rbb5b327508364485"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Home" sheetId="1" r:id="R31617882937f4688"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日の改善" sheetId="2" r:id="R507b5793db6d460b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善中" sheetId="3" r:id="R1d529b5efb754da0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ブログ診断" sheetId="4" r:id="R44c4095800284bf1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="処理ログ" sheetId="5" r:id="R01d3a14df5bd4f89"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定" sheetId="6" r:id="R8a8f451ebfc445f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SearchConsole_Data" sheetId="7" r:id="Rb34e9934355a4315"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Improvement_Queue" sheetId="8" r:id="R13c9e3a0d85c45d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Improvement_Log" sheetId="9" r:id="R141d70c6b3d64f38"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -345,7 +345,7 @@
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="34" t="str">
-        <x:v>SIMS-Blog-Manager Product 5.2.9</x:v>
+        <x:v>SIMS-Blog-Manager Product 5.2.10</x:v>
       </x:c>
       <x:c r="B1" s="35"/>
       <x:c r="C1" s="35"/>
@@ -5313,7 +5313,7 @@
         <x:v>Product Version</x:v>
       </x:c>
       <x:c r="B2" t="str">
-        <x:v>5.2.9</x:v>
+        <x:v>5.2.10</x:v>
       </x:c>
       <x:c r="C2" t="str">
         <x:v>UI/UX改訂版。既存データ互換。</x:v>
